--- a/data/raw/Data Dictionary (raw data).xlsx
+++ b/data/raw/Data Dictionary (raw data).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/GT/costed-NAPHS/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8016A5D7-0923-1240-8DA9-B3991415D5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A3465A-DCB0-634B-A270-2766422B2FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="460" yWindow="760" windowWidth="29780" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="242">
   <si>
     <t>Text</t>
   </si>
@@ -709,69 +709,10 @@
     <t xml:space="preserve">Afghanistan, Benin, Eritrea, Liberia, Myanmar, Nigeria, Sierra Leone, Timor-Leste, and Uganda </t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Afghanistan, Benin, Eritrea,  Liberia, Myanmar, Nigeria, Sierra Leone, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="9" tint="-0.499984740745262"/>
-        <rFont val="Source Sans 3"/>
-      </rPr>
-      <t>South Sudan</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Source Sans 3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF014D45"/>
-        <rFont val="Source Sans 3"/>
-      </rPr>
-      <t xml:space="preserve"> Sri Lanka</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Source Sans 3"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF014D45"/>
-        <rFont val="Source Sans 3"/>
-      </rPr>
-      <t>Tanzania</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Source Sans 3"/>
-      </rPr>
-      <t>, Timor-Leste, Uganda</t>
-    </r>
-  </si>
-  <si>
     <t>29 December, 2025</t>
   </si>
   <si>
     <t>Added additional summary cost data points ( Liberia, Myanmar, Nigeria, Sierra Leone, South Sudan, Sri Lanka, Tanzania, Timor-Leste, Uganda)</t>
-  </si>
-  <si>
-    <t>The data dictionary was last updated on 30 December, 2025</t>
   </si>
   <si>
     <t>30 December, 2025</t>
@@ -812,13 +753,25 @@
   </si>
   <si>
     <t>Multiple citations, see methods section of publication</t>
+  </si>
+  <si>
+    <t>The data dictionary was last updated on 28 April, 2026</t>
+  </si>
+  <si>
+    <t>Afghanistan, Benin, Cameroon, Eritrea,  Liberia, Myanmar, Nigeria, North Macedonia, Sierra Leone, South Sudan, Sri Lanka, Tanzania, Timor-Leste, Uganda</t>
+  </si>
+  <si>
+    <t>28  April, 2026</t>
+  </si>
+  <si>
+    <t>Updated lists of countries with summary-level data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -940,18 +893,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="Source Sans 3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="9" tint="-0.499984740745262"/>
-      <name val="Source Sans 3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF014D45"/>
       <name val="Source Sans 3"/>
     </font>
   </fonts>
@@ -1414,7 +1355,7 @@
     </row>
     <row r="4" spans="1:23" ht="22" customHeight="1">
       <c r="A4" s="35" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -1469,7 +1410,7 @@
     </row>
     <row r="9" spans="1:23" ht="40" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>205</v>
@@ -1484,7 +1425,7 @@
         <v>149</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
@@ -1506,7 +1447,7 @@
     </row>
     <row r="10" spans="1:23" ht="56" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>204</v>
@@ -1515,13 +1456,13 @@
         <v>220</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>149</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
@@ -1543,13 +1484,13 @@
     </row>
     <row r="11" spans="1:23" ht="56" customHeight="1">
       <c r="A11" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>231</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>233</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>190</v>
@@ -1558,7 +1499,7 @@
         <v>149</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
@@ -1580,13 +1521,13 @@
     </row>
     <row r="12" spans="1:23" ht="65" customHeight="1">
       <c r="A12" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>234</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>236</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>190</v>
@@ -1595,7 +1536,7 @@
         <v>149</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
@@ -3606,7 +3547,7 @@
     </row>
     <row r="4" spans="1:21" s="16" customFormat="1" ht="46" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>184</v>
@@ -3626,7 +3567,7 @@
     </row>
     <row r="5" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A5" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>161</v>
@@ -3661,7 +3602,7 @@
     </row>
     <row r="6" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A6" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>162</v>
@@ -3696,7 +3637,7 @@
     </row>
     <row r="7" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A7" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>163</v>
@@ -3731,7 +3672,7 @@
     </row>
     <row r="8" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A8" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>177</v>
@@ -3766,7 +3707,7 @@
     </row>
     <row r="9" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A9" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>173</v>
@@ -3801,7 +3742,7 @@
     </row>
     <row r="10" spans="1:21" s="16" customFormat="1" ht="84" customHeight="1">
       <c r="A10" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>197</v>
@@ -3832,7 +3773,7 @@
     </row>
     <row r="11" spans="1:21" s="16" customFormat="1" ht="84" customHeight="1">
       <c r="A11" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B11" s="20" t="s">
         <v>198</v>
@@ -3863,7 +3804,7 @@
     </row>
     <row r="12" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A12" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>164</v>
@@ -3898,7 +3839,7 @@
     </row>
     <row r="13" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A13" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B13" s="21" t="s">
         <v>206</v>
@@ -3933,7 +3874,7 @@
     </row>
     <row r="14" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A14" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B14" s="21" t="s">
         <v>161</v>
@@ -3968,7 +3909,7 @@
     </row>
     <row r="15" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A15" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B15" s="21" t="s">
         <v>207</v>
@@ -4003,7 +3944,7 @@
     </row>
     <row r="16" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A16" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>208</v>
@@ -4038,7 +3979,7 @@
     </row>
     <row r="17" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A17" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>177</v>
@@ -4073,7 +4014,7 @@
     </row>
     <row r="18" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A18" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B18" s="21" t="s">
         <v>173</v>
@@ -4108,7 +4049,7 @@
     </row>
     <row r="19" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A19" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B19" s="21" t="s">
         <v>209</v>
@@ -7705,10 +7646,10 @@
     </row>
     <row r="10" spans="1:19" ht="50" customHeight="1">
       <c r="A10" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="30" t="s">
         <v>224</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>225</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="28" t="s">
@@ -7734,10 +7675,10 @@
     </row>
     <row r="11" spans="1:19" ht="50" customHeight="1">
       <c r="A11" s="29" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="28" t="s">
@@ -7762,11 +7703,19 @@
       <c r="S11" s="12"/>
     </row>
     <row r="12" spans="1:19" ht="50" customHeight="1">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="A12" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>190</v>
+      </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
